--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -41795,6 +41795,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1802">
+      <c r="A1802" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1802" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1802" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1802" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1802" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1802" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1802" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -41818,6 +41818,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1803">
+      <c r="A1803" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1803" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1803" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1803" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1803" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1803" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1803" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -41841,6 +41841,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1804">
+      <c r="A1804" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1804" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1804" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1804" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1804" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1804" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1804" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -41864,6 +41864,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1805">
+      <c r="A1805" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1805" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1805" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1805" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1805" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1805" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1805" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -41728,7 +41728,7 @@
     </row>
     <row r="1799">
       <c r="A1799" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1799" t="n">
         <v>0</v>
@@ -41751,7 +41751,7 @@
     </row>
     <row r="1800">
       <c r="A1800" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1800" t="n">
         <v>0</v>
@@ -41774,7 +41774,7 @@
     </row>
     <row r="1801">
       <c r="A1801" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1801" t="n">
         <v>0</v>
@@ -41797,7 +41797,7 @@
     </row>
     <row r="1802">
       <c r="A1802" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1802" t="n">
         <v>0</v>
@@ -41820,7 +41820,7 @@
     </row>
     <row r="1803">
       <c r="A1803" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1803" t="n">
         <v>0</v>
@@ -41843,7 +41843,7 @@
     </row>
     <row r="1804">
       <c r="A1804" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1804" t="n">
         <v>0</v>
@@ -41866,7 +41866,7 @@
     </row>
     <row r="1805">
       <c r="A1805" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1805" t="n">
         <v>0</v>
@@ -41884,6 +41884,29 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1805" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1806" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1806" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1806" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1806" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1806" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1806" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -41910,6 +41910,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1807">
+      <c r="A1807" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1807" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1807" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1807" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1807" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1807" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1807" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1808" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1808" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="D1808" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="E1808" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="F1808" t="n">
+        <v>8.10000038146973</v>
+      </c>
+      <c r="G1808" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42002,6 +42002,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1811">
+      <c r="A1811" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1811" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1811" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="D1811" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F1811" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="G1811" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42025,6 +42025,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1812">
+      <c r="A1812" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1812" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1812" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="D1812" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F1812" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="G1812" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42048,6 +42048,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1813">
+      <c r="A1813" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1813" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1813" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="D1813" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="F1813" t="n">
+        <v>7.80000019073486</v>
+      </c>
+      <c r="G1813" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B1814" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1814" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1814" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1814"/>
+      <c r="G1814" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42087,7 +42087,9 @@
       <c r="E1814" t="n">
         <v>7.69999980926514</v>
       </c>
-      <c r="F1814"/>
+      <c r="F1814" t="n">
+        <v>7.69999980926514</v>
+      </c>
       <c r="G1814" t="s">
         <v>7</v>
       </c>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42094,6 +42094,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1815">
+      <c r="A1815" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B1815" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1815" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1815" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1815" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42117,6 +42117,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1816">
+      <c r="A1816" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1816" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1816" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1816" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1816" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1816" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42140,6 +42140,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1817">
+      <c r="A1817" s="1" t="n">
+        <v>46296.2916666667</v>
+      </c>
+      <c r="B1817" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1817" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1817" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1817" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1817" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42163,6 +42163,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1818">
+      <c r="A1818" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B1818" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1818" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1818" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1818" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1818" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42186,6 +42186,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1819">
+      <c r="A1819" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1819" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1819" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1819" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1819" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1819" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42209,6 +42209,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1820">
+      <c r="A1820" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1820" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1820" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1820" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1820" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1820" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1820" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42232,6 +42232,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1821">
+      <c r="A1821" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1821" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1821" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1821" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1821" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1821" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42255,6 +42255,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1822">
+      <c r="A1822" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1822" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1822" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1822" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1822" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1822" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42301,6 +42301,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1824">
+      <c r="A1824" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1824" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1824" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1824" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1824" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1824" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1824" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42324,6 +42324,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1825">
+      <c r="A1825" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1825" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1825" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1825" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E1825" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F1825" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1825" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42347,6 +42347,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1826">
+      <c r="A1826" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1826" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1826" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1826" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1826" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1826" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1826" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -42370,6 +42370,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1827">
+      <c r="A1827" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1827" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1827" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1827" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1827" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53390,6 +53390,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1829">
+      <c r="A1829" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1829" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1829" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1829" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1829" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1829" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1829" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53419,6 +53419,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1830">
+      <c r="A1830" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1830" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1830" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1830" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1830" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1830" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53448,6 +53448,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1831">
+      <c r="A1831" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1831" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1831" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1831" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1831" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1831" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53477,6 +53477,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1832">
+      <c r="A1832" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1832" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1832" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1832" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1832" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1832" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53506,6 +53506,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1833">
+      <c r="A1833" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1833" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1833" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1833" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1833" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1833" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1833" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53535,6 +53535,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1834">
+      <c r="A1834" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1834" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1834" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1834" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1834" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1834" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1834" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53564,6 +53564,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1835">
+      <c r="A1835" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1835" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1835" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1835" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1835" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1835" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53593,6 +53593,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1836">
+      <c r="A1836" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1836" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1836" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1836" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1836" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1836" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/COP.MI.xlsx
+++ b/data/COP.MI.xlsx
@@ -53622,6 +53622,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1837">
+      <c r="A1837" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1837" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1837" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D1837" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="G1837" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="H1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1837" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
